--- a/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0001T0006Z000C1N9_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0001T0006Z000C1N9_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>82.78395347209613</v>
+        <v>13.45239243921562</v>
       </c>
       <c r="D2" t="n">
-        <v>42.95346318982906</v>
+        <v>6.979937768347222</v>
       </c>
       <c r="E2" t="n">
-        <v>9.706699611138951</v>
+        <v>1.57733868681008</v>
       </c>
       <c r="F2" t="n">
-        <v>10.02574910431574</v>
+        <v>1.629184229451308</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>63.37055424981823</v>
+        <v>10.29771506559546</v>
       </c>
       <c r="D3" t="n">
-        <v>22.90196498119757</v>
+        <v>3.721569309444606</v>
       </c>
       <c r="E3" t="n">
-        <v>9.706699611138951</v>
+        <v>1.57733868681008</v>
       </c>
       <c r="F3" t="n">
-        <v>10.02574910431574</v>
+        <v>1.629184229451308</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
